--- a/public/flashcard_template.xlsx
+++ b/public/flashcard_template.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70F0531-3B12-4FB6-B097-DC7785B9EADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E76473-2429-46E1-BAA0-3C0ABCB6FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Buổi 2" sheetId="1" r:id="rId1"/>
     <sheet name="Buổi 3" sheetId="2" r:id="rId2"/>
     <sheet name="Buổi 4" sheetId="3" r:id="rId3"/>
     <sheet name="Buổi 5" sheetId="5" r:id="rId4"/>
+    <sheet name="Buổi 6" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="1140">
   <si>
     <t>English</t>
   </si>
@@ -2688,6 +2689,756 @@
   </si>
   <si>
     <t>basket</t>
+  </si>
+  <si>
+    <t>/ˈtredmɪl/</t>
+  </si>
+  <si>
+    <t>máy chạy bộ</t>
+  </si>
+  <si>
+    <t>He is running on the treadmill.</t>
+  </si>
+  <si>
+    <t>Anh ấy đang chạy trên máy chạy bộ.</t>
+  </si>
+  <si>
+    <t>/ˈbɑːtl/</t>
+  </si>
+  <si>
+    <t>chai</t>
+  </si>
+  <si>
+    <t>There is a bottle on the table.</t>
+  </si>
+  <si>
+    <t>Có một cái chai trên bàn.</t>
+  </si>
+  <si>
+    <t>/boʊl/</t>
+  </si>
+  <si>
+    <t>cái bát</t>
+  </si>
+  <si>
+    <t>She is holding a bowl.</t>
+  </si>
+  <si>
+    <t>Cô ấy đang cầm một cái bát.</t>
+  </si>
+  <si>
+    <t>/ˈmenjuː/</t>
+  </si>
+  <si>
+    <t>thực đơn</t>
+  </si>
+  <si>
+    <t>The waiter handed us the menu.</t>
+  </si>
+  <si>
+    <t>Người phục vụ đưa cho chúng tôi thực đơn.</t>
+  </si>
+  <si>
+    <t>/ˈteɪblklɔːθ/</t>
+  </si>
+  <si>
+    <t>khăn trải bàn</t>
+  </si>
+  <si>
+    <t>The tablecloth is white.</t>
+  </si>
+  <si>
+    <t>Khăn trải bàn màu trắng.</t>
+  </si>
+  <si>
+    <t>/ˈeriə/</t>
+  </si>
+  <si>
+    <t>khu vực</t>
+  </si>
+  <si>
+    <t>This area is very quiet.</t>
+  </si>
+  <si>
+    <t>Khu vực này rất yên tĩnh.</t>
+  </si>
+  <si>
+    <t>/miːl/</t>
+  </si>
+  <si>
+    <t>bữa ăn</t>
+  </si>
+  <si>
+    <t>They are enjoying a meal.</t>
+  </si>
+  <si>
+    <t>Họ đang thưởng thức một bữa ăn.</t>
+  </si>
+  <si>
+    <t>/pleɪt/</t>
+  </si>
+  <si>
+    <t>cái đĩa</t>
+  </si>
+  <si>
+    <t>The food is on the plate.</t>
+  </si>
+  <si>
+    <t>Thức ăn ở trên đĩa.</t>
+  </si>
+  <si>
+    <t>/ʌmˈbrelə/</t>
+  </si>
+  <si>
+    <t>cái ô</t>
+  </si>
+  <si>
+    <t>She is carrying an umbrella.</t>
+  </si>
+  <si>
+    <t>Cô ấy đang cầm ô.</t>
+  </si>
+  <si>
+    <t>/ˈkaʊntər/</t>
+  </si>
+  <si>
+    <t>cái quầy</t>
+  </si>
+  <si>
+    <t>He is standing at the counter.</t>
+  </si>
+  <si>
+    <t>Anh ấy đang đứng ở quầy.</t>
+  </si>
+  <si>
+    <t>/lɔːn/</t>
+  </si>
+  <si>
+    <t>bãi cỏ</t>
+  </si>
+  <si>
+    <t>The lawn is freshly cut.</t>
+  </si>
+  <si>
+    <t>Bãi cỏ vừa được cắt.</t>
+  </si>
+  <si>
+    <t>/pərˈfɔːrməns/</t>
+  </si>
+  <si>
+    <t>buổi biểu diễn</t>
+  </si>
+  <si>
+    <t>The performance was excellent.</t>
+  </si>
+  <si>
+    <t>Buổi biểu diễn rất tuyệt vời.</t>
+  </si>
+  <si>
+    <t>/taɪl/</t>
+  </si>
+  <si>
+    <t>gạch lát</t>
+  </si>
+  <si>
+    <t>The floor is covered with tiles.</t>
+  </si>
+  <si>
+    <t>Sàn nhà được lát gạch.</t>
+  </si>
+  <si>
+    <t>/saɪn/</t>
+  </si>
+  <si>
+    <t>biển báo</t>
+  </si>
+  <si>
+    <t>There is a sign near the road.</t>
+  </si>
+  <si>
+    <t>Có một biển báo gần con đường.</t>
+  </si>
+  <si>
+    <t>/ˈpʌdl/</t>
+  </si>
+  <si>
+    <t>vũng nước</t>
+  </si>
+  <si>
+    <t>A puddle is on the pavement.</t>
+  </si>
+  <si>
+    <t>Có một vũng nước trên vỉa hè.</t>
+  </si>
+  <si>
+    <t>/ˈpeɪvmənt/</t>
+  </si>
+  <si>
+    <t>vỉa hè</t>
+  </si>
+  <si>
+    <t>People are walking on the pavement.</t>
+  </si>
+  <si>
+    <t>Mọi người đang đi trên vỉa hè.</t>
+  </si>
+  <si>
+    <t>/kənˈstrʌkʃən ˈwɜːrkər/</t>
+  </si>
+  <si>
+    <t>công nhân xây dựng</t>
+  </si>
+  <si>
+    <t>The construction worker is wearing a hard hat.</t>
+  </si>
+  <si>
+    <t>Người công nhân xây dựng đang đội mũ bảo hộ.</t>
+  </si>
+  <si>
+    <t>/ˈentrəns/</t>
+  </si>
+  <si>
+    <t>lối vào</t>
+  </si>
+  <si>
+    <t>The entrance is crowded.</t>
+  </si>
+  <si>
+    <t>Lối vào rất đông.</t>
+  </si>
+  <si>
+    <t>/ˈkʌbərd/</t>
+  </si>
+  <si>
+    <t>tủ đựng đồ</t>
+  </si>
+  <si>
+    <t>The plates are in the cupboard.</t>
+  </si>
+  <si>
+    <t>Những chiếc đĩa ở trong tủ.</t>
+  </si>
+  <si>
+    <t>/juːˈtensl/</t>
+  </si>
+  <si>
+    <t>dụng cụ nhà bếp</t>
+  </si>
+  <si>
+    <t>She is washing a utensil.</t>
+  </si>
+  <si>
+    <t>Cô ấy đang rửa một dụng cụ nhà bếp.</t>
+  </si>
+  <si>
+    <t>/ˈaʊtlet/</t>
+  </si>
+  <si>
+    <t>ổ điện</t>
+  </si>
+  <si>
+    <t>The charger is plugged into the outlet.</t>
+  </si>
+  <si>
+    <t>Bộ sạc được cắm vào ổ điện.</t>
+  </si>
+  <si>
+    <t>/læmp/</t>
+  </si>
+  <si>
+    <t>đèn</t>
+  </si>
+  <si>
+    <t>The lamp is on the desk.</t>
+  </si>
+  <si>
+    <t>Chiếc đèn ở trên bàn.</t>
+  </si>
+  <si>
+    <t>/freɪm/</t>
+  </si>
+  <si>
+    <t>khung</t>
+  </si>
+  <si>
+    <t>The picture is in a frame.</t>
+  </si>
+  <si>
+    <t>Bức tranh ở trong khung.</t>
+  </si>
+  <si>
+    <t>/ˈlædər/</t>
+  </si>
+  <si>
+    <t>cái thang</t>
+  </si>
+  <si>
+    <t>He is standing on a ladder.</t>
+  </si>
+  <si>
+    <t>Anh ấy đang đứng trên thang.</t>
+  </si>
+  <si>
+    <t>/ˈpʌzl/</t>
+  </si>
+  <si>
+    <t>câu đố/ trò xếp hình</t>
+  </si>
+  <si>
+    <t>The child is doing a puzzle.</t>
+  </si>
+  <si>
+    <t>Đứa trẻ đang chơi trò xếp hình.</t>
+  </si>
+  <si>
+    <t>/ˈswetər/</t>
+  </si>
+  <si>
+    <t>áo len</t>
+  </si>
+  <si>
+    <t>She is wearing a sweater.</t>
+  </si>
+  <si>
+    <t>Cô ấy đang mặc áo len.</t>
+  </si>
+  <si>
+    <t>/ˈɡlæsɪz/</t>
+  </si>
+  <si>
+    <t>kính mắt</t>
+  </si>
+  <si>
+    <t>He is wearing glasses.</t>
+  </si>
+  <si>
+    <t>Anh ấy đang đeo kính.</t>
+  </si>
+  <si>
+    <t>/ˈhæmər/</t>
+  </si>
+  <si>
+    <t>cái búa</t>
+  </si>
+  <si>
+    <t>The hammer is on the floor.</t>
+  </si>
+  <si>
+    <t>Cái búa ở trên sàn.</t>
+  </si>
+  <si>
+    <t>/ɡeɪt/</t>
+  </si>
+  <si>
+    <t>cổng</t>
+  </si>
+  <si>
+    <t>The gate is open.</t>
+  </si>
+  <si>
+    <t>Cánh cổng đang mở.</t>
+  </si>
+  <si>
+    <t>/ˈreɪlɪŋ/</t>
+  </si>
+  <si>
+    <t>lan can</t>
+  </si>
+  <si>
+    <t>She is holding the railing.</t>
+  </si>
+  <si>
+    <t>Cô ấy đang vịn lan can.</t>
+  </si>
+  <si>
+    <t>/ˈkɑːləm/</t>
+  </si>
+  <si>
+    <t>cột</t>
+  </si>
+  <si>
+    <t>The building has tall columns.</t>
+  </si>
+  <si>
+    <t>Tòa nhà có những chiếc cột cao.</t>
+  </si>
+  <si>
+    <t>/ˈsɜːrvər/</t>
+  </si>
+  <si>
+    <t>người phục vụ</t>
+  </si>
+  <si>
+    <t>The server is carrying plates.</t>
+  </si>
+  <si>
+    <t>Người phục vụ đang bưng đĩa.</t>
+  </si>
+  <si>
+    <t>/ˈkeɪbl/</t>
+  </si>
+  <si>
+    <t>dây cáp</t>
+  </si>
+  <si>
+    <t>The cable is under the desk.</t>
+  </si>
+  <si>
+    <t>Dây cáp ở dưới bàn.</t>
+  </si>
+  <si>
+    <t>/stuːl/</t>
+  </si>
+  <si>
+    <t>ghế đẩu</t>
+  </si>
+  <si>
+    <t>He is sitting on a stool.</t>
+  </si>
+  <si>
+    <t>Anh ấy đang ngồi trên ghế đẩu.</t>
+  </si>
+  <si>
+    <t>/ˈkæbɪnət/</t>
+  </si>
+  <si>
+    <t>tủ</t>
+  </si>
+  <si>
+    <t>The cabinet is made of wood.</t>
+  </si>
+  <si>
+    <t>Chiếc tủ được làm bằng gỗ.</t>
+  </si>
+  <si>
+    <t>/ˈskæfoʊld/</t>
+  </si>
+  <si>
+    <t>giàn giáo</t>
+  </si>
+  <si>
+    <t>Workers are standing on the scaffold.</t>
+  </si>
+  <si>
+    <t>Công nhân đang đứng trên giàn giáo.</t>
+  </si>
+  <si>
+    <t>/ˈmɑːrkɪt stænd/</t>
+  </si>
+  <si>
+    <t>quầy hàng ở chợ</t>
+  </si>
+  <si>
+    <t>The fruit is displayed on the market stand.</t>
+  </si>
+  <si>
+    <t>Trái cây được bày trên quầy hàng.</t>
+  </si>
+  <si>
+    <t>/ˈpɪlər/</t>
+  </si>
+  <si>
+    <t>trụ cột</t>
+  </si>
+  <si>
+    <t>The roof is supported by pillars.</t>
+  </si>
+  <si>
+    <t>Mái nhà được chống đỡ bởi các trụ cột.</t>
+  </si>
+  <si>
+    <t>/ˈpoʊdiəm/</t>
+  </si>
+  <si>
+    <t>bục phát biểu</t>
+  </si>
+  <si>
+    <t>The speaker is standing at the podium.</t>
+  </si>
+  <si>
+    <t>Diễn giả đang đứng ở bục phát biểu.</t>
+  </si>
+  <si>
+    <t>/pɪr/</t>
+  </si>
+  <si>
+    <t>bến tàu/ cầu tàu</t>
+  </si>
+  <si>
+    <t>People are walking on the pier.</t>
+  </si>
+  <si>
+    <t>Mọi người đang đi trên cầu tàu.</t>
+  </si>
+  <si>
+    <t>/kreɪt/</t>
+  </si>
+  <si>
+    <t>thùng gỗ / sọt</t>
+  </si>
+  <si>
+    <t>The apples are in a crate.</t>
+  </si>
+  <si>
+    <t>Những quả táo ở trong thùng.</t>
+  </si>
+  <si>
+    <t>/ˈstɪrɪŋ wiːl/</t>
+  </si>
+  <si>
+    <t>vô lăng</t>
+  </si>
+  <si>
+    <t>He is holding the steering wheel.</t>
+  </si>
+  <si>
+    <t>Anh ấy đang cầm vô lăng.</t>
+  </si>
+  <si>
+    <t>/ˈpætioʊ/</t>
+  </si>
+  <si>
+    <t>sân hiên</t>
+  </si>
+  <si>
+    <t>They are sitting on the patio.</t>
+  </si>
+  <si>
+    <t>Họ đang ngồi ở sân hiên.</t>
+  </si>
+  <si>
+    <t>/kɜːrb/</t>
+  </si>
+  <si>
+    <t>lề đường</t>
+  </si>
+  <si>
+    <t>The car is parked by the curb.</t>
+  </si>
+  <si>
+    <t>Chiếc xe được đậu bên lề đường.</t>
+  </si>
+  <si>
+    <t>/ræmp/</t>
+  </si>
+  <si>
+    <t>đường dốc</t>
+  </si>
+  <si>
+    <t>The wheelchair is on the ramp.</t>
+  </si>
+  <si>
+    <t>Chiếc xe lăn đang ở trên đường dốc.</t>
+  </si>
+  <si>
+    <t>/ˈwɪndoʊ ledʒ/</t>
+  </si>
+  <si>
+    <t>bệ cửa sổ</t>
+  </si>
+  <si>
+    <t>A plant is on the window ledge.</t>
+  </si>
+  <si>
+    <t>Một chậu cây ở trên bệ cửa sổ.</t>
+  </si>
+  <si>
+    <t>/ˈʃædoʊ/</t>
+  </si>
+  <si>
+    <t>bóng / bóng râm</t>
+  </si>
+  <si>
+    <t>The tree casts a shadow.</t>
+  </si>
+  <si>
+    <t>Cái cây tạo ra bóng râm.</t>
+  </si>
+  <si>
+    <t>/ˈpærəlel/</t>
+  </si>
+  <si>
+    <t>song song</t>
+  </si>
+  <si>
+    <t>The lines are parallel.</t>
+  </si>
+  <si>
+    <t>Các đường thẳng song song.</t>
+  </si>
+  <si>
+    <t>/ˈlæmpˌpoʊst/</t>
+  </si>
+  <si>
+    <t>cột đèn</t>
+  </si>
+  <si>
+    <t>The lamppost is near the road.</t>
+  </si>
+  <si>
+    <t>Cột đèn ở gần con đường.</t>
+  </si>
+  <si>
+    <t>/ˈkɔːrɪdɔːr/</t>
+  </si>
+  <si>
+    <t>hành lang</t>
+  </si>
+  <si>
+    <t>She is walking down the corridor.</t>
+  </si>
+  <si>
+    <t>Cô ấy đang đi dọc hành lang.</t>
+  </si>
+  <si>
+    <t>treadmill</t>
+  </si>
+  <si>
+    <t>bottle</t>
+  </si>
+  <si>
+    <t>bowl</t>
+  </si>
+  <si>
+    <t>menu</t>
+  </si>
+  <si>
+    <t>tablecloth</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t>meal</t>
+  </si>
+  <si>
+    <t>plate</t>
+  </si>
+  <si>
+    <t>umbrella</t>
+  </si>
+  <si>
+    <t>counter</t>
+  </si>
+  <si>
+    <t>lawn</t>
+  </si>
+  <si>
+    <t>performance</t>
+  </si>
+  <si>
+    <t>tile</t>
+  </si>
+  <si>
+    <t>sign</t>
+  </si>
+  <si>
+    <t>puddle</t>
+  </si>
+  <si>
+    <t>pavement</t>
+  </si>
+  <si>
+    <t>construction worker</t>
+  </si>
+  <si>
+    <t>entrance</t>
+  </si>
+  <si>
+    <t>cupboard</t>
+  </si>
+  <si>
+    <t>utensil</t>
+  </si>
+  <si>
+    <t>outlet</t>
+  </si>
+  <si>
+    <t>lamp</t>
+  </si>
+  <si>
+    <t>frame</t>
+  </si>
+  <si>
+    <t>ladder</t>
+  </si>
+  <si>
+    <t>puzzle</t>
+  </si>
+  <si>
+    <t>sweater</t>
+  </si>
+  <si>
+    <t>glasses</t>
+  </si>
+  <si>
+    <t>hammer</t>
+  </si>
+  <si>
+    <t>gate</t>
+  </si>
+  <si>
+    <t>railing</t>
+  </si>
+  <si>
+    <t>column</t>
+  </si>
+  <si>
+    <t>server</t>
+  </si>
+  <si>
+    <t>cable</t>
+  </si>
+  <si>
+    <t>stool</t>
+  </si>
+  <si>
+    <t>cabinet</t>
+  </si>
+  <si>
+    <t>scaffold</t>
+  </si>
+  <si>
+    <t>market stand</t>
+  </si>
+  <si>
+    <t>pillar</t>
+  </si>
+  <si>
+    <t>podium</t>
+  </si>
+  <si>
+    <t>pier</t>
+  </si>
+  <si>
+    <t>crate</t>
+  </si>
+  <si>
+    <t>steering wheel</t>
+  </si>
+  <si>
+    <t>patio</t>
+  </si>
+  <si>
+    <t>curb</t>
+  </si>
+  <si>
+    <t>ramp</t>
+  </si>
+  <si>
+    <t>window ledge</t>
+  </si>
+  <si>
+    <t>shadow</t>
+  </si>
+  <si>
+    <t>parallel</t>
+  </si>
+  <si>
+    <t>lamppost</t>
+  </si>
+  <si>
+    <t>corridor</t>
   </si>
 </sst>
 </file>
@@ -6697,4 +7448,887 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1BB0A6-53C6-476C-8815-BCA74E0E94A5}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/flashcard_template.xlsx
+++ b/public/flashcard_template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E76473-2429-46E1-BAA0-3C0ABCB6FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C814FDA-6BF0-4D27-94A8-2DB4573D3671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Buổi 2" sheetId="1" r:id="rId1"/>
@@ -13,13 +13,14 @@
     <sheet name="Buổi 4" sheetId="3" r:id="rId3"/>
     <sheet name="Buổi 5" sheetId="5" r:id="rId4"/>
     <sheet name="Buổi 6" sheetId="6" r:id="rId5"/>
+    <sheet name="Buổi 7" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="1387">
   <si>
     <t>English</t>
   </si>
@@ -3439,6 +3440,747 @@
   </si>
   <si>
     <t>corridor</t>
+  </si>
+  <si>
+    <t>/ˈvesl/</t>
+  </si>
+  <si>
+    <t>tàu / bình chứa</t>
+  </si>
+  <si>
+    <t>The vessel is sailing on the sea.</t>
+  </si>
+  <si>
+    <t>Con tàu đang đi trên biển.</t>
+  </si>
+  <si>
+    <t>/kəˈnæl/</t>
+  </si>
+  <si>
+    <t>kênh đào</t>
+  </si>
+  <si>
+    <t>Boats travel along the canal.</t>
+  </si>
+  <si>
+    <t>Thuyền đi dọc kênh đào.</t>
+  </si>
+  <si>
+    <t>/ˈbætər/</t>
+  </si>
+  <si>
+    <t>bột (làm bánh)</t>
+  </si>
+  <si>
+    <t>She mixes the batter.</t>
+  </si>
+  <si>
+    <t>Cô ấy trộn bột.</t>
+  </si>
+  <si>
+    <t>/treɪl/</t>
+  </si>
+  <si>
+    <t>đường mòn</t>
+  </si>
+  <si>
+    <t>They walk along the trail.</t>
+  </si>
+  <si>
+    <t>Họ đi dọc đường mòn.</t>
+  </si>
+  <si>
+    <t>/pəˈvɪliən/</t>
+  </si>
+  <si>
+    <t>nhà chòi, đình</t>
+  </si>
+  <si>
+    <t>People sit in the pavilion.</t>
+  </si>
+  <si>
+    <t>Mọi người ngồi trong chòi.</t>
+  </si>
+  <si>
+    <t>/dɜːrt/</t>
+  </si>
+  <si>
+    <t>đất, bụi bẩn</t>
+  </si>
+  <si>
+    <t>His shoes are covered in dirt.</t>
+  </si>
+  <si>
+    <t>Giày anh ấy dính đất.</t>
+  </si>
+  <si>
+    <t>/ˈpɪtʃər/</t>
+  </si>
+  <si>
+    <t>bình nước</t>
+  </si>
+  <si>
+    <t>The pitcher is on the table.</t>
+  </si>
+  <si>
+    <t>Bình nước ở trên bàn.</t>
+  </si>
+  <si>
+    <t>/dʒɑːr/</t>
+  </si>
+  <si>
+    <t>Hũ,lọ</t>
+  </si>
+  <si>
+    <t>The cookies are in the jar.</t>
+  </si>
+  <si>
+    <t>Bánh ở trong lọ.</t>
+  </si>
+  <si>
+    <t>/ˈspekˌteɪtər/</t>
+  </si>
+  <si>
+    <t>khán giả</t>
+  </si>
+  <si>
+    <t>Spectators watch the game.</t>
+  </si>
+  <si>
+    <t>Khán giả xem trận đấu.</t>
+  </si>
+  <si>
+    <t>/ˈtʃekpɔɪnt ˈbæriər/</t>
+  </si>
+  <si>
+    <t>rào chắn kiểm soát</t>
+  </si>
+  <si>
+    <t>The car stops at the checkpoint barrier.</t>
+  </si>
+  <si>
+    <t>Xe dừng ở rào chắn.</t>
+  </si>
+  <si>
+    <t>/ˈbækpæk/</t>
+  </si>
+  <si>
+    <t>ba lô</t>
+  </si>
+  <si>
+    <t>He carries a backpack.</t>
+  </si>
+  <si>
+    <t>Anh ấy mang ba lô.</t>
+  </si>
+  <si>
+    <t>/ˈsuːtkeɪs/</t>
+  </si>
+  <si>
+    <t>vali</t>
+  </si>
+  <si>
+    <t>She packs a suitcase.</t>
+  </si>
+  <si>
+    <t>Cô ấy đóng vali.</t>
+  </si>
+  <si>
+    <t>/ˈʃuːleɪs/</t>
+  </si>
+  <si>
+    <t>dây giày</t>
+  </si>
+  <si>
+    <t>He ties his shoelaces.</t>
+  </si>
+  <si>
+    <t>Anh ấy buộc dây giày.</t>
+  </si>
+  <si>
+    <t>/ˈvendər/</t>
+  </si>
+  <si>
+    <t>người bán hàng</t>
+  </si>
+  <si>
+    <t>The vendor sells fruit.</t>
+  </si>
+  <si>
+    <t>Người bán bán trái cây.</t>
+  </si>
+  <si>
+    <t>/sɪŋk/</t>
+  </si>
+  <si>
+    <t>bồn rửa</t>
+  </si>
+  <si>
+    <t>The sink is full of dishes.</t>
+  </si>
+  <si>
+    <t>Bồn rửa đầy bát đĩa.</t>
+  </si>
+  <si>
+    <t>/ˈmaɪkrəweɪv ˈʌvn/</t>
+  </si>
+  <si>
+    <t>lò vi sóng</t>
+  </si>
+  <si>
+    <t>She uses the microwave oven.</t>
+  </si>
+  <si>
+    <t>Cô ấy dùng lò vi sóng.</t>
+  </si>
+  <si>
+    <t>/klɔːθ/</t>
+  </si>
+  <si>
+    <t>khăn vải</t>
+  </si>
+  <si>
+    <t>He cleans with a cloth.</t>
+  </si>
+  <si>
+    <t>Anh ấy lau bằng khăn.</t>
+  </si>
+  <si>
+    <t>/ˈfɔːsɪt/</t>
+  </si>
+  <si>
+    <t>vòi nước</t>
+  </si>
+  <si>
+    <t>Water runs from the faucet.</t>
+  </si>
+  <si>
+    <t>Nước chảy từ vòi.</t>
+  </si>
+  <si>
+    <t>/ˈtaʊəl/</t>
+  </si>
+  <si>
+    <t>khăn</t>
+  </si>
+  <si>
+    <t>She dries her hands with a towel.</t>
+  </si>
+  <si>
+    <t>Cô ấy lau tay bằng khăn.</t>
+  </si>
+  <si>
+    <t>/ˈeɪprən/</t>
+  </si>
+  <si>
+    <t>tạp dề</t>
+  </si>
+  <si>
+    <t>She wears an apron.</t>
+  </si>
+  <si>
+    <t>Cô ấy mặc tạp dề.</t>
+  </si>
+  <si>
+    <t>/pɑːt/</t>
+  </si>
+  <si>
+    <t>nồi</t>
+  </si>
+  <si>
+    <t>The pot is on the stove.</t>
+  </si>
+  <si>
+    <t>Nồi ở trên bếp.</t>
+  </si>
+  <si>
+    <t>/bentʃ/</t>
+  </si>
+  <si>
+    <t>ghế dài</t>
+  </si>
+  <si>
+    <t>They sit on a bench.</t>
+  </si>
+  <si>
+    <t>Họ ngồi trên ghế dài.</t>
+  </si>
+  <si>
+    <t>/ˈfriːzər/</t>
+  </si>
+  <si>
+    <t>tủ đông</t>
+  </si>
+  <si>
+    <t>The food is in the freezer.</t>
+  </si>
+  <si>
+    <t>Thức ăn ở trong tủ đông.</t>
+  </si>
+  <si>
+    <t>/ˈɑːrtwɜːrk/</t>
+  </si>
+  <si>
+    <t>tác phẩm nghệ thuật</t>
+  </si>
+  <si>
+    <t>The artwork is displayed.</t>
+  </si>
+  <si>
+    <t>Tác phẩm được trưng bày.</t>
+  </si>
+  <si>
+    <t>/ˈdresər/</t>
+  </si>
+  <si>
+    <t>tủ quần áo</t>
+  </si>
+  <si>
+    <t>Clothes are in the dresser.</t>
+  </si>
+  <si>
+    <t>Quần áo ở trong tủ.</t>
+  </si>
+  <si>
+    <t>/ˈkɔːrnər/</t>
+  </si>
+  <si>
+    <t>góc</t>
+  </si>
+  <si>
+    <t>The chair is in the corner.</t>
+  </si>
+  <si>
+    <t>Ghế ở góc phòng.</t>
+  </si>
+  <si>
+    <t>/dɔːr ˈhændl/</t>
+  </si>
+  <si>
+    <t>tay nắm cửa</t>
+  </si>
+  <si>
+    <t>He turns the door handle.</t>
+  </si>
+  <si>
+    <t>Anh ấy xoay tay nắm cửa.</t>
+  </si>
+  <si>
+    <t>/wiːld ˈlʌɡɪdʒ/</t>
+  </si>
+  <si>
+    <t>vali có bánh xe</t>
+  </si>
+  <si>
+    <t>She pulls wheeled luggage.</t>
+  </si>
+  <si>
+    <t>Cô ấy kéo vali.</t>
+  </si>
+  <si>
+    <t>/ˈwaɪtbɔːrd/</t>
+  </si>
+  <si>
+    <t>bảng trắng</t>
+  </si>
+  <si>
+    <t>The teacher writes on the whiteboard.</t>
+  </si>
+  <si>
+    <t>Giáo viên viết trên bảng trắng.</t>
+  </si>
+  <si>
+    <t>/ˈfɜːrnɪtʃər/</t>
+  </si>
+  <si>
+    <t>đồ nội thất</t>
+  </si>
+  <si>
+    <t>The furniture is modern.</t>
+  </si>
+  <si>
+    <t>Đồ nội thất hiện đại.</t>
+  </si>
+  <si>
+    <t>/ˈlɑːbi/</t>
+  </si>
+  <si>
+    <t>sảnh chờ</t>
+  </si>
+  <si>
+    <t>They wait in the lobby.</t>
+  </si>
+  <si>
+    <t>Họ chờ ở sảnh.</t>
+  </si>
+  <si>
+    <t>/ˈhelmɪt/</t>
+  </si>
+  <si>
+    <t>mũ bảo hiểm</t>
+  </si>
+  <si>
+    <t>He wears a helmet.</t>
+  </si>
+  <si>
+    <t>Anh ấy đội mũ bảo hiểm.</t>
+  </si>
+  <si>
+    <t>/ˈdɑːkjəmənt/</t>
+  </si>
+  <si>
+    <t>tài liệu</t>
+  </si>
+  <si>
+    <t>She reads a document.</t>
+  </si>
+  <si>
+    <t>Cô ấy đọc tài liệu.</t>
+  </si>
+  <si>
+    <t>/ˈbaɪndər/</t>
+  </si>
+  <si>
+    <t>bìa kẹp tài liệu, bìa hồ sơ</t>
+  </si>
+  <si>
+    <t>The papers are in a binder.</t>
+  </si>
+  <si>
+    <t>Giấy ở trong bìa.</t>
+  </si>
+  <si>
+    <t>/væn/</t>
+  </si>
+  <si>
+    <t>xe tải nhỏ</t>
+  </si>
+  <si>
+    <t>The van is parked outside.</t>
+  </si>
+  <si>
+    <t>Xe tải nhỏ đậu bên ngoài.</t>
+  </si>
+  <si>
+    <t>/ʃrʌb/</t>
+  </si>
+  <si>
+    <t>The shrub is green.</t>
+  </si>
+  <si>
+    <t>/ˌɪntərˈsekʃən/</t>
+  </si>
+  <si>
+    <t>ngã tư</t>
+  </si>
+  <si>
+    <t>Cars stop at the intersection.</t>
+  </si>
+  <si>
+    <t>Xe dừng ở ngã tư.</t>
+  </si>
+  <si>
+    <t>/ˈtaɪər/</t>
+  </si>
+  <si>
+    <t>lốp xe</t>
+  </si>
+  <si>
+    <t>The tire is flat.</t>
+  </si>
+  <si>
+    <t>Lốp xe bị xẹp.</t>
+  </si>
+  <si>
+    <t>/tent/</t>
+  </si>
+  <si>
+    <t>lều</t>
+  </si>
+  <si>
+    <t>They sleep in a tent.</t>
+  </si>
+  <si>
+    <t>Họ ngủ trong lều.</t>
+  </si>
+  <si>
+    <t>/bræntʃ/</t>
+  </si>
+  <si>
+    <t>cành cây</t>
+  </si>
+  <si>
+    <t>The branch is broken.</t>
+  </si>
+  <si>
+    <t>Cành cây bị gãy.</t>
+  </si>
+  <si>
+    <t>/brɪk/</t>
+  </si>
+  <si>
+    <t>gạch</t>
+  </si>
+  <si>
+    <t>The wall is made of brick.</t>
+  </si>
+  <si>
+    <t>Tường làm bằng gạch.</t>
+  </si>
+  <si>
+    <t>/ˈhɔːlweɪ/</t>
+  </si>
+  <si>
+    <t>He walks down the hallway.</t>
+  </si>
+  <si>
+    <t>Anh ấy đi dọc hành lang.</t>
+  </si>
+  <si>
+    <t>/ræk/</t>
+  </si>
+  <si>
+    <t>giá</t>
+  </si>
+  <si>
+    <t>Clothes are on the rack.</t>
+  </si>
+  <si>
+    <t>Quần áo trên giá.</t>
+  </si>
+  <si>
+    <t>/ˈpɪloʊ/</t>
+  </si>
+  <si>
+    <t>gối</t>
+  </si>
+  <si>
+    <t>She rests her head on a pillow.</t>
+  </si>
+  <si>
+    <t>Cô ấy tựa đầu lên gối.</t>
+  </si>
+  <si>
+    <t>/ˈɡroʊsəri/</t>
+  </si>
+  <si>
+    <t>đồ tạp hóa</t>
+  </si>
+  <si>
+    <t>She buys groceries.</t>
+  </si>
+  <si>
+    <t>Cô ấy mua đồ tạp hóa.</t>
+  </si>
+  <si>
+    <t>/swɪtʃ/</t>
+  </si>
+  <si>
+    <t>công tắc</t>
+  </si>
+  <si>
+    <t>He turns on the switch.</t>
+  </si>
+  <si>
+    <t>Anh ấy bật công tắc.</t>
+  </si>
+  <si>
+    <t>/ˈflaʊərbed/</t>
+  </si>
+  <si>
+    <t>bồn hoa</t>
+  </si>
+  <si>
+    <t>The flowers grow in the flowerbed.</t>
+  </si>
+  <si>
+    <t>Hoa mọc trong bồn.</t>
+  </si>
+  <si>
+    <t>/liːvz/</t>
+  </si>
+  <si>
+    <t>lá cây</t>
+  </si>
+  <si>
+    <t>Leaves fall from the tree.</t>
+  </si>
+  <si>
+    <t>Lá rơi từ cây.</t>
+  </si>
+  <si>
+    <t>/wɑːtʃ stræp/</t>
+  </si>
+  <si>
+    <t>dây đồng hồ</t>
+  </si>
+  <si>
+    <t>The watch strap is broken.</t>
+  </si>
+  <si>
+    <t>Dây đồng hồ bị hỏng.</t>
+  </si>
+  <si>
+    <t>/skriːn/</t>
+  </si>
+  <si>
+    <t>màn hình</t>
+  </si>
+  <si>
+    <t>The screen is bright.</t>
+  </si>
+  <si>
+    <t>Màn hình sáng.</t>
+  </si>
+  <si>
+    <t>vessel</t>
+  </si>
+  <si>
+    <t>canal</t>
+  </si>
+  <si>
+    <t>batter</t>
+  </si>
+  <si>
+    <t>trail</t>
+  </si>
+  <si>
+    <t>pavilion</t>
+  </si>
+  <si>
+    <t>dirt</t>
+  </si>
+  <si>
+    <t>pitcher</t>
+  </si>
+  <si>
+    <t>jar</t>
+  </si>
+  <si>
+    <t>spectator</t>
+  </si>
+  <si>
+    <t>checkpoint barrier</t>
+  </si>
+  <si>
+    <t>backpack</t>
+  </si>
+  <si>
+    <t>suitcase</t>
+  </si>
+  <si>
+    <t>shoelace</t>
+  </si>
+  <si>
+    <t>vendor</t>
+  </si>
+  <si>
+    <t>sink</t>
+  </si>
+  <si>
+    <t>microwave oven</t>
+  </si>
+  <si>
+    <t>cloth</t>
+  </si>
+  <si>
+    <t>faucet</t>
+  </si>
+  <si>
+    <t>towel</t>
+  </si>
+  <si>
+    <t>apron</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>bench</t>
+  </si>
+  <si>
+    <t>freezer</t>
+  </si>
+  <si>
+    <t>artwork</t>
+  </si>
+  <si>
+    <t>dresser</t>
+  </si>
+  <si>
+    <t>corner</t>
+  </si>
+  <si>
+    <t>door handle</t>
+  </si>
+  <si>
+    <t>wheeled luggage</t>
+  </si>
+  <si>
+    <t>whiteboard</t>
+  </si>
+  <si>
+    <t>furniture</t>
+  </si>
+  <si>
+    <t>lobby</t>
+  </si>
+  <si>
+    <t>helmet</t>
+  </si>
+  <si>
+    <t>document</t>
+  </si>
+  <si>
+    <t>binder</t>
+  </si>
+  <si>
+    <t>van</t>
+  </si>
+  <si>
+    <t>shrub</t>
+  </si>
+  <si>
+    <t>intersection</t>
+  </si>
+  <si>
+    <t>tire</t>
+  </si>
+  <si>
+    <t>tent</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>hallway</t>
+  </si>
+  <si>
+    <t>rack</t>
+  </si>
+  <si>
+    <t>pillow</t>
+  </si>
+  <si>
+    <t>grocery</t>
+  </si>
+  <si>
+    <t>switch</t>
+  </si>
+  <si>
+    <t>flowerbed</t>
+  </si>
+  <si>
+    <t>leaves</t>
+  </si>
+  <si>
+    <t>watch strap</t>
+  </si>
+  <si>
+    <t>screen</t>
   </si>
 </sst>
 </file>
@@ -8107,7 +8849,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>1127</v>
       </c>
@@ -8326,6 +9068,889 @@
       </c>
       <c r="E51" s="2" t="s">
         <v>1089</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFF2592-A8C1-479D-9FA7-CED5734C7CF8}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>1336</v>
       </c>
     </row>
   </sheetData>

--- a/public/flashcard_template.xlsx
+++ b/public/flashcard_template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C814FDA-6BF0-4D27-94A8-2DB4573D3671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B87B670-8627-4662-8B7E-21CC9E7DCF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Buổi 2" sheetId="1" r:id="rId1"/>
@@ -14,13 +14,14 @@
     <sheet name="Buổi 5" sheetId="5" r:id="rId4"/>
     <sheet name="Buổi 6" sheetId="6" r:id="rId5"/>
     <sheet name="Buổi 7" sheetId="7" r:id="rId6"/>
+    <sheet name="Buổi 8" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="1387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="1630">
   <si>
     <t>English</t>
   </si>
@@ -4181,6 +4182,735 @@
   </si>
   <si>
     <t>screen</t>
+  </si>
+  <si>
+    <t>/ˈviːəkl/</t>
+  </si>
+  <si>
+    <t>phương tiện xe (nói chung)</t>
+  </si>
+  <si>
+    <t>The vehicle is parked outside.</t>
+  </si>
+  <si>
+    <t>Phương tiện được đậu ở bên ngoài.</t>
+  </si>
+  <si>
+    <t>/ˈɔːtəməbiːl/</t>
+  </si>
+  <si>
+    <t>ô tô</t>
+  </si>
+  <si>
+    <t>The automobile is very expensive.</t>
+  </si>
+  <si>
+    <t>Chiếc ô tô rất đắt.</t>
+  </si>
+  <si>
+    <t>/trʌk/</t>
+  </si>
+  <si>
+    <t>xe tải</t>
+  </si>
+  <si>
+    <t>The truck is carrying goods.</t>
+  </si>
+  <si>
+    <t>Chiếc xe tải đang chở hàng.</t>
+  </si>
+  <si>
+    <t>/kʌp/</t>
+  </si>
+  <si>
+    <t>tách, cốc</t>
+  </si>
+  <si>
+    <t>She is holding a cup.</t>
+  </si>
+  <si>
+    <t>Cô ấy đang cầm một cái cốc.</t>
+  </si>
+  <si>
+    <t>/snoʊ/</t>
+  </si>
+  <si>
+    <t>tuyết</t>
+  </si>
+  <si>
+    <t>Snow covers the ground.</t>
+  </si>
+  <si>
+    <t>Tuyết phủ kín mặt đất.</t>
+  </si>
+  <si>
+    <t>/ˈʃʌvl/</t>
+  </si>
+  <si>
+    <t>cái xẻng</t>
+  </si>
+  <si>
+    <t>The shovel is leaning against the wall.</t>
+  </si>
+  <si>
+    <t>Cái xẻng đang tựa vào tường.</t>
+  </si>
+  <si>
+    <t>/ˈɡæləri/</t>
+  </si>
+  <si>
+    <t>phòng trưng bày</t>
+  </si>
+  <si>
+    <t>They visited an art gallery.</t>
+  </si>
+  <si>
+    <t>Họ đã đến thăm một phòng trưng bày nghệ thuật.</t>
+  </si>
+  <si>
+    <t>/ˌkɑːnvərˈseɪʃn/</t>
+  </si>
+  <si>
+    <t>cuộc trò chuyện</t>
+  </si>
+  <si>
+    <t>They are having a conversation.</t>
+  </si>
+  <si>
+    <t>Họ đang trò chuyện.</t>
+  </si>
+  <si>
+    <t>/ˈsoʊfə/</t>
+  </si>
+  <si>
+    <t>ghế sofa</t>
+  </si>
+  <si>
+    <t>The sofa is near the window.</t>
+  </si>
+  <si>
+    <t>Ghế sofa ở gần cửa sổ.</t>
+  </si>
+  <si>
+    <t>/ˈpɪktʃər/</t>
+  </si>
+  <si>
+    <t>A picture is hanging on the wall.</t>
+  </si>
+  <si>
+    <t>Một bức tranh đang treo trên tường.</t>
+  </si>
+  <si>
+    <t>/ɡəˈrɑːʒ/</t>
+  </si>
+  <si>
+    <t>nhà để xe</t>
+  </si>
+  <si>
+    <t>The car is in the garage.</t>
+  </si>
+  <si>
+    <t>Chiếc xe ở trong nhà để xe.</t>
+  </si>
+  <si>
+    <t>/kloʊðz ˈhæŋər/</t>
+  </si>
+  <si>
+    <t>mắc áo</t>
+  </si>
+  <si>
+    <t>The shirt is on a clothes hanger.</t>
+  </si>
+  <si>
+    <t>Chiếc áo ở trên mắc áo.</t>
+  </si>
+  <si>
+    <t>/ˈentriweɪ/</t>
+  </si>
+  <si>
+    <t>Shoes are placed in the entryway.</t>
+  </si>
+  <si>
+    <t>Giày được đặt ở lối vào.</t>
+  </si>
+  <si>
+    <t>/rʌɡ/</t>
+  </si>
+  <si>
+    <t>tấm thảm</t>
+  </si>
+  <si>
+    <t>The rug is under the table.</t>
+  </si>
+  <si>
+    <t>Tấm thảm ở dưới bàn.</t>
+  </si>
+  <si>
+    <t>/laɪt ˈfɪkstʃər/</t>
+  </si>
+  <si>
+    <t>thiết bị chiếu sáng</t>
+  </si>
+  <si>
+    <t>The light fixture hangs from the ceiling.</t>
+  </si>
+  <si>
+    <t>Thiết bị chiếu sáng treo trên trần nhà.</t>
+  </si>
+  <si>
+    <t>/kɔːrd/</t>
+  </si>
+  <si>
+    <t>sợi dây</t>
+  </si>
+  <si>
+    <t>The cord is plugged into the outlet.</t>
+  </si>
+  <si>
+    <t>Sợi dây được cắm vào ổ điện.</t>
+  </si>
+  <si>
+    <t>/ˈbʌtn/</t>
+  </si>
+  <si>
+    <t>nút bấm, cúc áo</t>
+  </si>
+  <si>
+    <t>One button is missing from the shirt.</t>
+  </si>
+  <si>
+    <t>Một chiếc cúc áo bị thiếu trên áo sơ mi.</t>
+  </si>
+  <si>
+    <t>/ˈnoʊtɪs/</t>
+  </si>
+  <si>
+    <t>thông báo</t>
+  </si>
+  <si>
+    <t>There is a notice on the door.</t>
+  </si>
+  <si>
+    <t>Có một thông báo trên cửa.</t>
+  </si>
+  <si>
+    <t>/ˈbʊlətɪn bɔːrd/</t>
+  </si>
+  <si>
+    <t>bảng tin</t>
+  </si>
+  <si>
+    <t>The bulletin board is full of papers.</t>
+  </si>
+  <si>
+    <t>Bảng tin đầy giấy tờ.</t>
+  </si>
+  <si>
+    <t>/ˈkʌtɪŋ bɔːrd/</t>
+  </si>
+  <si>
+    <t>thớt</t>
+  </si>
+  <si>
+    <t>The vegetables are on the cutting board.</t>
+  </si>
+  <si>
+    <t>Rau ở trên thớt.</t>
+  </si>
+  <si>
+    <t>/bɪn/</t>
+  </si>
+  <si>
+    <t>thùng rác</t>
+  </si>
+  <si>
+    <t>The bin is next to the desk.</t>
+  </si>
+  <si>
+    <t>Thùng rác ở cạnh bàn làm việc.</t>
+  </si>
+  <si>
+    <t>/wʊd/</t>
+  </si>
+  <si>
+    <t>gỗ</t>
+  </si>
+  <si>
+    <t>The chair is made of wood.</t>
+  </si>
+  <si>
+    <t>Chiếc ghế được làm bằng gỗ.</t>
+  </si>
+  <si>
+    <t>/lɔːɡ/</t>
+  </si>
+  <si>
+    <t>khúc gỗ</t>
+  </si>
+  <si>
+    <t>A log is lying on the ground.</t>
+  </si>
+  <si>
+    <t>Một khúc gỗ đang nằm trên mặt đất.</t>
+  </si>
+  <si>
+    <t>/ˈkænəpi/</t>
+  </si>
+  <si>
+    <t>mái hiên</t>
+  </si>
+  <si>
+    <t>The canopy provides shade.</t>
+  </si>
+  <si>
+    <t>Mái hiên tạo bóng mát.</t>
+  </si>
+  <si>
+    <t>/ˈɔːnɪŋ/</t>
+  </si>
+  <si>
+    <t>mái che</t>
+  </si>
+  <si>
+    <t>The shop has a striped awning.</t>
+  </si>
+  <si>
+    <t>Cửa hàng có một mái che sọc.</t>
+  </si>
+  <si>
+    <t>/ˈeskəleɪtər/</t>
+  </si>
+  <si>
+    <t>thang cuốn</t>
+  </si>
+  <si>
+    <t>People are standing on the escalator.</t>
+  </si>
+  <si>
+    <t>Mọi người đang đứng trên thang cuốn.</t>
+  </si>
+  <si>
+    <t>/ˈʃʌtl bʌs/</t>
+  </si>
+  <si>
+    <t>xe buýt đưa đón</t>
+  </si>
+  <si>
+    <t>The shuttle bus stops at the hotel.</t>
+  </si>
+  <si>
+    <t>Xe buýt đưa đón dừng ở khách sạn.</t>
+  </si>
+  <si>
+    <t>/ˈelɪveɪtər/</t>
+  </si>
+  <si>
+    <t>thang máy</t>
+  </si>
+  <si>
+    <t>They are waiting for the elevator.</t>
+  </si>
+  <si>
+    <t>Họ đang chờ thang máy.</t>
+  </si>
+  <si>
+    <t>/ˈʃelvɪŋ ˈjuːnɪt/</t>
+  </si>
+  <si>
+    <t>kệ sách</t>
+  </si>
+  <si>
+    <t>Books are arranged on the shelving unit.</t>
+  </si>
+  <si>
+    <t>Sách được sắp xếp trên kệ.</t>
+  </si>
+  <si>
+    <t>/ruːf/</t>
+  </si>
+  <si>
+    <t>mái nhà</t>
+  </si>
+  <si>
+    <t>Snow is covering the roof.</t>
+  </si>
+  <si>
+    <t>Tuyết đang phủ trên mái nhà.</t>
+  </si>
+  <si>
+    <t>/ʃiːt/</t>
+  </si>
+  <si>
+    <t>tấm (kim loại, giấy)</t>
+  </si>
+  <si>
+    <t>He is holding a sheet of paper.</t>
+  </si>
+  <si>
+    <t>Anh ấy đang cầm một tờ giấy.</t>
+  </si>
+  <si>
+    <t>/fiːld/</t>
+  </si>
+  <si>
+    <t>cánh đồng</t>
+  </si>
+  <si>
+    <t>They are walking across the field.</t>
+  </si>
+  <si>
+    <t>Họ đang đi băng qua cánh đồng.</t>
+  </si>
+  <si>
+    <t>/ˈstrʌktʃər/</t>
+  </si>
+  <si>
+    <t>cấu trúc</t>
+  </si>
+  <si>
+    <t>The structure is made of steel.</t>
+  </si>
+  <si>
+    <t>Cấu trúc được làm bằng thép.</t>
+  </si>
+  <si>
+    <t>/ʃɜːrt/</t>
+  </si>
+  <si>
+    <t>áo sơ mi</t>
+  </si>
+  <si>
+    <t>He is wearing a white shirt.</t>
+  </si>
+  <si>
+    <t>Anh ấy đang mặc một chiếc áo sơ mi trắng.</t>
+  </si>
+  <si>
+    <t>/ˈmɑːnɪtər/</t>
+  </si>
+  <si>
+    <t>The monitor is on the desk.</t>
+  </si>
+  <si>
+    <t>Màn hình ở trên bàn.</t>
+  </si>
+  <si>
+    <t>/brɪdʒ/</t>
+  </si>
+  <si>
+    <t>cây cầu</t>
+  </si>
+  <si>
+    <t>Cars are crossing the bridge.</t>
+  </si>
+  <si>
+    <t>Xe đang đi qua cầu.</t>
+  </si>
+  <si>
+    <t>/ˈkɑːrɡoʊ/</t>
+  </si>
+  <si>
+    <t>The ship is carrying cargo.</t>
+  </si>
+  <si>
+    <t>Con tàu đang chở hàng hóa.</t>
+  </si>
+  <si>
+    <t>/boʊt/</t>
+  </si>
+  <si>
+    <t>thuyền</t>
+  </si>
+  <si>
+    <t>A boat is floating on the lake.</t>
+  </si>
+  <si>
+    <t>Một chiếc thuyền đang nổi trên hồ.</t>
+  </si>
+  <si>
+    <t>/kəˈnuː/</t>
+  </si>
+  <si>
+    <t>thuyền ca-nô</t>
+  </si>
+  <si>
+    <t>They are paddling a canoe.</t>
+  </si>
+  <si>
+    <t>Họ đang chèo một chiếc ca-nô.</t>
+  </si>
+  <si>
+    <t>/ˈmaʊntən/</t>
+  </si>
+  <si>
+    <t>núi</t>
+  </si>
+  <si>
+    <t>The mountain is covered with snow.</t>
+  </si>
+  <si>
+    <t>Ngọn núi được phủ tuyết.</t>
+  </si>
+  <si>
+    <t>/pɑːnd/</t>
+  </si>
+  <si>
+    <t>ao</t>
+  </si>
+  <si>
+    <t>Ducks are swimming in the pond.</t>
+  </si>
+  <si>
+    <t>Vịt đang bơi trong ao.</t>
+  </si>
+  <si>
+    <t>/kaʊtʃ/</t>
+  </si>
+  <si>
+    <t>The cat is sleeping on the couch.</t>
+  </si>
+  <si>
+    <t>Con mèo đang ngủ trên ghế dài.</t>
+  </si>
+  <si>
+    <t>/veɪs/</t>
+  </si>
+  <si>
+    <t>bình hoa</t>
+  </si>
+  <si>
+    <t>The vase is filled with flowers.</t>
+  </si>
+  <si>
+    <t>Bình hoa được cắm đầy hoa.</t>
+  </si>
+  <si>
+    <t>/ˈbælkəni/</t>
+  </si>
+  <si>
+    <t>ban công</t>
+  </si>
+  <si>
+    <t>She is standing on the balcony.</t>
+  </si>
+  <si>
+    <t>Cô ấy đang đứng ở ban công.</t>
+  </si>
+  <si>
+    <t>/buːts/</t>
+  </si>
+  <si>
+    <t>ủng, bốt</t>
+  </si>
+  <si>
+    <t>The boots are by the door.</t>
+  </si>
+  <si>
+    <t>Đôi ủng ở cạnh cửa.</t>
+  </si>
+  <si>
+    <t>/pæθ/</t>
+  </si>
+  <si>
+    <t>con đường</t>
+  </si>
+  <si>
+    <t>They are walking along the path.</t>
+  </si>
+  <si>
+    <t>Họ đang đi dọc theo con đường.</t>
+  </si>
+  <si>
+    <t>/ˈtʌnl/</t>
+  </si>
+  <si>
+    <t>đường hầm</t>
+  </si>
+  <si>
+    <t>The train is entering the tunnel.</t>
+  </si>
+  <si>
+    <t>Tàu đang đi vào đường hầm.</t>
+  </si>
+  <si>
+    <t>/ˈpætərn/</t>
+  </si>
+  <si>
+    <t>hoa văn</t>
+  </si>
+  <si>
+    <t>The fabric has a floral pattern.</t>
+  </si>
+  <si>
+    <t>Tấm vải có hoa văn hoa.</t>
+  </si>
+  <si>
+    <t>/ˈskaɪskreɪpər/</t>
+  </si>
+  <si>
+    <t>tòa nhà chọc trời</t>
+  </si>
+  <si>
+    <t>That skyscraper is very tall.</t>
+  </si>
+  <si>
+    <t>Tòa nhà chọc trời đó rất cao.</t>
+  </si>
+  <si>
+    <t>/ˈwɔːkɪŋ stɪk/</t>
+  </si>
+  <si>
+    <t>gậy đi bộ</t>
+  </si>
+  <si>
+    <t>He is using a walking stick.</t>
+  </si>
+  <si>
+    <t>Ông ấy đang dùng gậy đi bộ.</t>
+  </si>
+  <si>
+    <t>vehicle</t>
+  </si>
+  <si>
+    <t>automobile</t>
+  </si>
+  <si>
+    <t>truck</t>
+  </si>
+  <si>
+    <t>cup</t>
+  </si>
+  <si>
+    <t>snow</t>
+  </si>
+  <si>
+    <t>gallery</t>
+  </si>
+  <si>
+    <t>conversation</t>
+  </si>
+  <si>
+    <t>sofa</t>
+  </si>
+  <si>
+    <t>picture</t>
+  </si>
+  <si>
+    <t>garage</t>
+  </si>
+  <si>
+    <t>clothes hanger</t>
+  </si>
+  <si>
+    <t>entryway</t>
+  </si>
+  <si>
+    <t>rug</t>
+  </si>
+  <si>
+    <t>light fixture</t>
+  </si>
+  <si>
+    <t>cord</t>
+  </si>
+  <si>
+    <t>notice</t>
+  </si>
+  <si>
+    <t>bulletin board</t>
+  </si>
+  <si>
+    <t>cutting board</t>
+  </si>
+  <si>
+    <t>bin</t>
+  </si>
+  <si>
+    <t>wood</t>
+  </si>
+  <si>
+    <t>log</t>
+  </si>
+  <si>
+    <t>canopy</t>
+  </si>
+  <si>
+    <t>awning</t>
+  </si>
+  <si>
+    <t>escalator</t>
+  </si>
+  <si>
+    <t>shuttle bus</t>
+  </si>
+  <si>
+    <t>elevator</t>
+  </si>
+  <si>
+    <t>shelving unit</t>
+  </si>
+  <si>
+    <t>roof</t>
+  </si>
+  <si>
+    <t>sheet</t>
+  </si>
+  <si>
+    <t>field</t>
+  </si>
+  <si>
+    <t>structure</t>
+  </si>
+  <si>
+    <t>shirt</t>
+  </si>
+  <si>
+    <t>monitor</t>
+  </si>
+  <si>
+    <t>bridge</t>
+  </si>
+  <si>
+    <t>cargo</t>
+  </si>
+  <si>
+    <t>boat</t>
+  </si>
+  <si>
+    <t>canoe</t>
+  </si>
+  <si>
+    <t>mountain</t>
+  </si>
+  <si>
+    <t>pond</t>
+  </si>
+  <si>
+    <t>couch</t>
+  </si>
+  <si>
+    <t>vase</t>
+  </si>
+  <si>
+    <t>balcony</t>
+  </si>
+  <si>
+    <t>boots</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>tunnel</t>
+  </si>
+  <si>
+    <t>pattern</t>
+  </si>
+  <si>
+    <t>skyscraper</t>
+  </si>
+  <si>
+    <t>walking stick</t>
   </si>
 </sst>
 </file>
@@ -9956,4 +10686,887 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2559B38D-E947-4744-BDAF-B7E6ED6D273E}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/flashcard_template.xlsx
+++ b/public/flashcard_template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B87B670-8627-4662-8B7E-21CC9E7DCF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA86B093-5F2D-4FF6-99C6-540E7166FE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23136" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Buổi 2" sheetId="1" r:id="rId1"/>
@@ -15,13 +15,14 @@
     <sheet name="Buổi 6" sheetId="6" r:id="rId5"/>
     <sheet name="Buổi 7" sheetId="7" r:id="rId6"/>
     <sheet name="Buổi 8" sheetId="8" r:id="rId7"/>
+    <sheet name="Voucablry" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="1630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="1688">
   <si>
     <t>English</t>
   </si>
@@ -4911,6 +4912,180 @@
   </si>
   <si>
     <t>walking stick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intended </t>
+  </si>
+  <si>
+    <t>dự định</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> motivation </t>
+  </si>
+  <si>
+    <t>động lực</t>
+  </si>
+  <si>
+    <t>improved</t>
+  </si>
+  <si>
+    <t>cải thiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">appointing </t>
+  </si>
+  <si>
+    <t>bổ nhiệm</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> financed </t>
+  </si>
+  <si>
+    <t>được tài trợ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> directed </t>
+  </si>
+  <si>
+    <t>được hướng dẫn</t>
+  </si>
+  <si>
+    <t>lời khen ngợi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> compliment</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> promotion </t>
+  </si>
+  <si>
+    <t>khuyến mãi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">encouraged </t>
+  </si>
+  <si>
+    <t>động viên</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> expected </t>
+  </si>
+  <si>
+    <t>hy vọng</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> permitting </t>
+  </si>
+  <si>
+    <t>cho phép</t>
+  </si>
+  <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>đánh giá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reliability </t>
+  </si>
+  <si>
+    <t>độ tin cậy</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> inspect </t>
+  </si>
+  <si>
+    <t>thanh tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> removal </t>
+  </si>
+  <si>
+    <t>loại bỏ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deserved </t>
+  </si>
+  <si>
+    <t>xứng đáng</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> increases </t>
+  </si>
+  <si>
+    <t>tăng lên</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> variety </t>
+  </si>
+  <si>
+    <t>đa dạng</t>
+  </si>
+  <si>
+    <t>proposal</t>
+  </si>
+  <si>
+    <t>sự đề xuất</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> suitable </t>
+  </si>
+  <si>
+    <t>thích hợp</t>
+  </si>
+  <si>
+    <t>extensive</t>
+  </si>
+  <si>
+    <t>rộng rãi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comparable </t>
+  </si>
+  <si>
+    <t>tương đương</t>
+  </si>
+  <si>
+    <t>favorable</t>
+  </si>
+  <si>
+    <t>thuận lợi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> qualifications </t>
+  </si>
+  <si>
+    <t>trình độ chuyên môn</t>
+  </si>
+  <si>
+    <t>necessary</t>
+  </si>
+  <si>
+    <t>cần thiết</t>
+  </si>
+  <si>
+    <t>become familiar with</t>
+  </si>
+  <si>
+    <t>làm quen với</t>
+  </si>
+  <si>
+    <t>internationally recognized</t>
+  </si>
+  <si>
+    <t>được công nhận quốc tế</t>
+  </si>
+  <si>
+    <t>years of service</t>
+  </si>
+  <si>
+    <t>số năm phục vụ</t>
+  </si>
+  <si>
+    <t>years in operation</t>
+  </si>
+  <si>
+    <t>năm hoạt động</t>
   </si>
 </sst>
 </file>
@@ -11569,4 +11744,499 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A623959F-F63E-46EA-94E2-0B35AAEEBDCC}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/flashcard_template.xlsx
+++ b/public/flashcard_template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA86B093-5F2D-4FF6-99C6-540E7166FE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC36D04F-B797-44BC-9320-1CBB61473392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23136" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23040" yWindow="1092" windowWidth="21600" windowHeight="11292" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Buổi 2" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="1688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="1689">
   <si>
     <t>English</t>
   </si>
@@ -5086,6 +5086,9 @@
   </si>
   <si>
     <t>năm hoạt động</t>
+  </si>
+  <si>
+    <t>Test</t>
   </si>
 </sst>
 </file>
@@ -11780,6 +11783,9 @@
         <v>1631</v>
       </c>
       <c r="D2" s="6"/>
+      <c r="E2" t="s">
+        <v>1688</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
